--- a/artfynd/A 41134-2025 artfynd.xlsx
+++ b/artfynd/A 41134-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>127415041</v>
       </c>
       <c r="B7" t="n">
-        <v>91912</v>
+        <v>91915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127415063</v>
       </c>
       <c r="B8" t="n">
-        <v>91912</v>
+        <v>91915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41134-2025 artfynd.xlsx
+++ b/artfynd/A 41134-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>127415041</v>
       </c>
       <c r="B7" t="n">
-        <v>91915</v>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127415063</v>
       </c>
       <c r="B8" t="n">
-        <v>91915</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41134-2025 artfynd.xlsx
+++ b/artfynd/A 41134-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>127415041</v>
       </c>
       <c r="B7" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127415063</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41134-2025 artfynd.xlsx
+++ b/artfynd/A 41134-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>127415041</v>
       </c>
       <c r="B7" t="n">
-        <v>91924</v>
+        <v>91925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127415063</v>
       </c>
       <c r="B8" t="n">
-        <v>91924</v>
+        <v>91925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41134-2025 artfynd.xlsx
+++ b/artfynd/A 41134-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>127415041</v>
       </c>
       <c r="B7" t="n">
-        <v>91925</v>
+        <v>91926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127415063</v>
       </c>
       <c r="B8" t="n">
-        <v>91925</v>
+        <v>91926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41134-2025 artfynd.xlsx
+++ b/artfynd/A 41134-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150959</v>
+        <v>121150958</v>
       </c>
       <c r="B2" t="n">
-        <v>79723</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766177</v>
+        <v>766166</v>
       </c>
       <c r="R2" t="n">
-        <v>7446009</v>
+        <v>7446058</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150960</v>
+        <v>127415041</v>
       </c>
       <c r="B3" t="n">
-        <v>79723</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766218</v>
+        <v>766173</v>
       </c>
       <c r="R3" t="n">
-        <v>7446024</v>
+        <v>7446009</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150956</v>
+        <v>127415063</v>
       </c>
       <c r="B4" t="n">
-        <v>79723</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766198</v>
+        <v>766167</v>
       </c>
       <c r="R4" t="n">
-        <v>7445978</v>
+        <v>7446055</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150957</v>
+        <v>121150956</v>
       </c>
       <c r="B5" t="n">
-        <v>79723</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766163</v>
+        <v>766198</v>
       </c>
       <c r="R5" t="n">
-        <v>7446013</v>
+        <v>7445978</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,42 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150958</v>
+        <v>121150957</v>
       </c>
       <c r="B6" t="n">
-        <v>91275</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>766166</v>
+        <v>766163</v>
       </c>
       <c r="R6" t="n">
-        <v>7446058</v>
+        <v>7446013</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127415041</v>
+        <v>121150959</v>
       </c>
       <c r="B7" t="n">
-        <v>91926</v>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1269,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>766173</v>
+        <v>766177</v>
       </c>
       <c r="R7" t="n">
         <v>7446009</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1336,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127415063</v>
+        <v>121150960</v>
       </c>
       <c r="B8" t="n">
-        <v>91926</v>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,13 +1350,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>766167</v>
+        <v>766218</v>
       </c>
       <c r="R8" t="n">
-        <v>7446055</v>
+        <v>7446024</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,12 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1439,6 +1414,112 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121150961</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Leipojärvi, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>766225</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7446057</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41134-2025 artfynd.xlsx
+++ b/artfynd/A 41134-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415063</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150956</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150959</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150960</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,8 +1560,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150961</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>